--- a/data/trans_dic/P15D$ingresado-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P15D$ingresado-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, el ingreso en hospital o clínica</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, el ingreso en hospital o clínica (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,38; 21,86</t>
+          <t>5,43; 21,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 22,05</t>
+          <t>2,45; 21,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,63; 30,73</t>
+          <t>7,98; 29,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,19</t>
+          <t>0,0; 29,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 19,16</t>
+          <t>2,2; 19,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,21; 27,56</t>
+          <t>5,11; 26,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,78; 21,42</t>
+          <t>7,6; 20,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,14</t>
+          <t>0,0; 13,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,6; 17,55</t>
+          <t>4,99; 17,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 20,81</t>
+          <t>6,22; 19,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,32; 23,56</t>
+          <t>9,97; 22,61</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,55; 35,33</t>
+          <t>7,73; 34,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 12,78</t>
+          <t>1,39; 11,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,1; 27,25</t>
+          <t>6,16; 26,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,64; 35,66</t>
+          <t>9,19; 33,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,63; 22,35</t>
+          <t>5,72; 20,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,88; 30,07</t>
+          <t>6,7; 30,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,83; 30,4</t>
+          <t>5,37; 29,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,6; 23,49</t>
+          <t>4,55; 21,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 13,75</t>
+          <t>4,39; 13,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,73; 23,63</t>
+          <t>8,32; 24,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,98; 26,51</t>
+          <t>9,89; 26,44</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,63; 48,63</t>
+          <t>8,71; 47,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,31; 24,33</t>
+          <t>5,9; 23,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 25,1</t>
+          <t>2,77; 24,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,7; 33,77</t>
+          <t>7,59; 36,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,48</t>
+          <t>0,0; 25,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,6; 20,43</t>
+          <t>3,65; 20,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,53</t>
+          <t>0,0; 21,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,29; 17,42</t>
+          <t>3,49; 18,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,21; 29,52</t>
+          <t>6,43; 29,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,81; 18,86</t>
+          <t>6,3; 18,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 18,24</t>
+          <t>3,1; 16,71</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 20,4</t>
+          <t>6,7; 20,85</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 25,66</t>
+          <t>2,49; 25,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 13,13</t>
+          <t>2,08; 14,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 19,04</t>
+          <t>3,08; 20,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 22,32</t>
+          <t>4,7; 22,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,04</t>
+          <t>0,0; 27,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,46</t>
+          <t>0,0; 8,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 18,86</t>
+          <t>1,83; 17,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,31; 17,01</t>
+          <t>5,27; 16,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 21,92</t>
+          <t>3,41; 21,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 9,33</t>
+          <t>1,83; 9,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,94; 14,73</t>
+          <t>4,17; 15,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,27; 15,86</t>
+          <t>6,64; 15,91</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,29; 21,8</t>
+          <t>8,34; 22,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,39; 12,23</t>
+          <t>5,57; 12,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,22; 16,05</t>
+          <t>7,27; 16,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,21; 22,01</t>
+          <t>11,2; 23,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 10,86</t>
+          <t>1,89; 12,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,93; 11,83</t>
+          <t>4,92; 12,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,6; 16,52</t>
+          <t>6,48; 16,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,93; 16,86</t>
+          <t>8,2; 17,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,36; 15,32</t>
+          <t>6,68; 15,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 10,68</t>
+          <t>6,04; 10,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,95; 14,74</t>
+          <t>8,0; 14,66</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,86; 17,97</t>
+          <t>10,83; 17,61</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, el ingreso en hospital o clínica</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, el ingreso en hospital o clínica (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1806</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3177; 12902</t>
+          <t>3206; 12806</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1036; 9173</t>
+          <t>1021; 8977</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3872; 13792</t>
+          <t>3582; 13084</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5108</t>
+          <t>0; 4743</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1153; 10056</t>
+          <t>1157; 10211</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3022; 13415</t>
+          <t>2485; 12822</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3365; 9264</t>
+          <t>3287; 9004</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5078</t>
+          <t>0; 5130</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6244; 19572</t>
+          <t>5562; 19596</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5559; 18790</t>
+          <t>5612; 18016</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9098; 20759</t>
+          <t>8782; 19927</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4085; 15114</t>
+          <t>3306; 14805</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1004; 10104</t>
+          <t>1100; 9370</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4292; 16480</t>
+          <t>3724; 16075</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7136; 23912</t>
+          <t>6161; 22756</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1981</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4082; 16211</t>
+          <t>4151; 14976</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2787; 14256</t>
+          <t>3178; 14689</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3337; 17398</t>
+          <t>3071; 16657</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4087; 17131</t>
+          <t>3317; 15696</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6812; 20845</t>
+          <t>6656; 20824</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9417; 25488</t>
+          <t>8976; 26046</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12404; 32948</t>
+          <t>12289; 32858</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2054; 11577</t>
+          <t>2073; 11231</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3624; 13980</t>
+          <t>3391; 13681</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1040; 9203</t>
+          <t>1015; 8915</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1959; 9871</t>
+          <t>2218; 10673</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4939</t>
+          <t>0; 6266</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2054; 11654</t>
+          <t>2080; 11731</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6480</t>
+          <t>0; 6649</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1450; 7685</t>
+          <t>1541; 8329</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2975; 14147</t>
+          <t>3081; 14135</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7801; 21599</t>
+          <t>7212; 20992</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2070; 12446</t>
+          <t>2117; 11398</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4644; 14960</t>
+          <t>4913; 15291</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>818; 8648</t>
+          <t>839; 8452</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1038; 11579</t>
+          <t>1833; 12929</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1774; 11594</t>
+          <t>1878; 12416</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3078; 13142</t>
+          <t>2767; 12976</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 7117</t>
+          <t>0; 6487</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6836</t>
+          <t>0; 6341</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1101; 11810</t>
+          <t>1146; 10915</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3662; 11743</t>
+          <t>3638; 11681</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2285; 12580</t>
+          <t>1955; 12189</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2980; 14970</t>
+          <t>2932; 14827</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4869; 18190</t>
+          <t>5144; 18580</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8017; 20290</t>
+          <t>8493; 20349</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10199; 26830</t>
+          <t>10271; 27270</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15289; 34716</t>
+          <t>15800; 35781</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14421; 32040</t>
+          <t>14519; 32869</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22434; 44043</t>
+          <t>22408; 46561</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1180; 10186</t>
+          <t>1777; 11797</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12527; 30078</t>
+          <t>12509; 31099</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12554; 31425</t>
+          <t>12332; 30864</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16941; 36007</t>
+          <t>17521; 36713</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13786; 33224</t>
+          <t>14495; 33396</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31596; 57467</t>
+          <t>32517; 58572</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30994; 57455</t>
+          <t>31206; 57173</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>44915; 74353</t>
+          <t>44812; 72856</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15D$ingresado-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P15D$ingresado-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -722,57 +722,57 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,43; 21,7</t>
+          <t>4,83; 22,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 21,58</t>
+          <t>2,46; 21,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,98; 29,15</t>
+          <t>8,86; 30,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,9</t>
+          <t>0,0; 31,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 19,46</t>
+          <t>2,19; 18,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 26,34</t>
+          <t>6,19; 26,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,6; 20,82</t>
+          <t>8,33; 22,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,27</t>
+          <t>0,0; 15,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,99; 17,58</t>
+          <t>5,69; 16,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,22; 19,96</t>
+          <t>6,64; 20,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,97; 22,61</t>
+          <t>9,76; 23,43</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,73; 34,61</t>
+          <t>9,38; 35,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 11,85</t>
+          <t>1,25; 11,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,16; 26,58</t>
+          <t>6,84; 26,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,19; 33,93</t>
+          <t>9,71; 33,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,37 +882,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 20,65</t>
+          <t>5,84; 21,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 30,98</t>
+          <t>5,57; 30,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 29,1</t>
+          <t>6,35; 32,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 21,53</t>
+          <t>5,48; 21,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 13,73</t>
+          <t>4,74; 13,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,32; 24,14</t>
+          <t>8,86; 24,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,89; 26,44</t>
+          <t>9,91; 26,33</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,71; 47,18</t>
+          <t>8,7; 45,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,9; 23,81</t>
+          <t>5,23; 25,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 24,31</t>
+          <t>2,84; 25,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,59; 36,51</t>
+          <t>6,49; 33,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,99</t>
+          <t>0,0; 22,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,65; 20,56</t>
+          <t>3,46; 20,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,07</t>
+          <t>0,0; 24,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 18,88</t>
+          <t>3,38; 19,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,43; 29,5</t>
+          <t>6,0; 27,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 18,33</t>
+          <t>6,35; 18,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 16,71</t>
+          <t>3,08; 17,34</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,7; 20,85</t>
+          <t>6,83; 19,74</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 25,07</t>
+          <t>2,53; 24,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 14,66</t>
+          <t>2,04; 13,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 20,39</t>
+          <t>2,94; 19,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 22,04</t>
+          <t>5,06; 22,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,38</t>
+          <t>0,0; 26,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,77</t>
+          <t>0,0; 8,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 17,43</t>
+          <t>2,05; 18,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,27; 16,92</t>
+          <t>5,93; 17,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 21,24</t>
+          <t>3,48; 20,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 9,24</t>
+          <t>1,35; 9,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 15,04</t>
+          <t>4,03; 14,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,64; 15,91</t>
+          <t>7,57; 17,76</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,34; 22,16</t>
+          <t>7,97; 22,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,57; 12,61</t>
+          <t>5,44; 12,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,27; 16,46</t>
+          <t>6,93; 16,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,2; 23,27</t>
+          <t>11,57; 22,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 12,58</t>
+          <t>2,01; 11,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,92; 12,23</t>
+          <t>5,32; 12,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,48; 16,22</t>
+          <t>6,92; 16,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,2; 17,19</t>
+          <t>8,29; 16,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,68; 15,4</t>
+          <t>6,56; 15,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,04; 10,88</t>
+          <t>5,99; 10,77</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,0; 14,66</t>
+          <t>8,15; 14,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,83; 17,61</t>
+          <t>11,15; 17,78</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13406</t>
+          <t>15118</t>
         </is>
       </c>
     </row>
@@ -1650,57 +1650,57 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3206; 12806</t>
+          <t>2851; 13303</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1021; 8977</t>
+          <t>1023; 9065</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3582; 13084</t>
+          <t>4402; 15300</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4743</t>
+          <t>0; 4960</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1157; 10211</t>
+          <t>1148; 9858</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2485; 12822</t>
+          <t>3014; 13092</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3287; 9004</t>
+          <t>3910; 10524</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5130</t>
+          <t>0; 6118</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5562; 19596</t>
+          <t>6346; 18672</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5612; 18016</t>
+          <t>5991; 18714</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8782; 19927</t>
+          <t>9432; 22637</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>14181</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7399</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20233</t>
+          <t>22382</t>
         </is>
       </c>
     </row>
@@ -1853,22 +1853,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3306; 14805</t>
+          <t>4014; 15205</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1100; 9370</t>
+          <t>986; 9473</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3724; 16075</t>
+          <t>4134; 15897</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6161; 22756</t>
+          <t>7262; 25212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1878,37 +1878,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4151; 14976</t>
+          <t>4239; 15654</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3178; 14689</t>
+          <t>2642; 14377</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3071; 16657</t>
+          <t>3991; 20116</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3317; 15696</t>
+          <t>3996; 15894</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6656; 20824</t>
+          <t>7181; 20782</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8976; 26046</t>
+          <t>9563; 26682</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12289; 32858</t>
+          <t>13635; 36232</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>9808</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2073; 11231</t>
+          <t>2072; 10908</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3391; 13681</t>
+          <t>3007; 14401</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1015; 8915</t>
+          <t>1040; 9245</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2218; 10673</t>
+          <t>2139; 11089</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6266</t>
+          <t>0; 5388</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2080; 11731</t>
+          <t>1974; 11572</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6649</t>
+          <t>0; 7663</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1541; 8329</t>
+          <t>1673; 9487</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3081; 14135</t>
+          <t>2873; 13325</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7212; 20992</t>
+          <t>7274; 20660</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2117; 11398</t>
+          <t>2102; 11833</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4913; 15291</t>
+          <t>5630; 16275</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>7710</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>7895</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13380</t>
+          <t>15605</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>839; 8452</t>
+          <t>852; 8256</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1833; 12929</t>
+          <t>1804; 12324</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1878; 12416</t>
+          <t>1790; 12092</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2767; 12976</t>
+          <t>3218; 14413</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6487</t>
+          <t>0; 6195</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6341</t>
+          <t>0; 6254</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1146; 10915</t>
+          <t>1287; 11437</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3638; 11681</t>
+          <t>4331; 12692</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1955; 12189</t>
+          <t>1998; 11936</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2932; 14827</t>
+          <t>2161; 15604</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5144; 18580</t>
+          <t>4983; 17824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8493; 20349</t>
+          <t>10337; 24242</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32074</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24002</t>
+          <t>26913</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>56076</t>
+          <t>62913</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10271; 27270</t>
+          <t>9806; 27330</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15800; 35781</t>
+          <t>15444; 35229</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14519; 32869</t>
+          <t>13828; 32443</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22408; 46561</t>
+          <t>25581; 49570</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1777; 11797</t>
+          <t>1882; 10619</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12509; 31099</t>
+          <t>13537; 30608</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12332; 30864</t>
+          <t>13168; 32182</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17521; 36713</t>
+          <t>19249; 38188</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14495; 33396</t>
+          <t>14220; 33122</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32517; 58572</t>
+          <t>32220; 57975</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31206; 57173</t>
+          <t>31789; 56715</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>44812; 72856</t>
+          <t>50546; 80578</t>
         </is>
       </c>
     </row>
